--- a/resources/templates/standard/M1100-02.xlsx
+++ b/resources/templates/standard/M1100-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>설비 비가동 시간 관리 대장</t>
   </si>
@@ -524,12 +527,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -564,21 +569,21 @@
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM1" s="3"/>
       <c r="AN1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4"/>
       <c r="AQ1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
       <c r="AT1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -685,29 +690,29 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
@@ -717,7 +722,7 @@
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
       <c r="W4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
@@ -727,7 +732,7 @@
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
@@ -736,7 +741,7 @@
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM4" s="3"/>
       <c r="AN4" s="3"/>
@@ -745,7 +750,7 @@
       <c r="AQ4" s="3"/>
       <c r="AR4" s="3"/>
       <c r="AS4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT4" s="4"/>
       <c r="AU4" s="4"/>
